--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\EdgeDownload\Luban\luban_examples-main\luban_examples-main\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0CA3F46-AC08-4B7D-80B0-FBE78AB3DF36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7455A8C-3AB8-4CAA-A390-DDE235D81E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6020" yWindow="5500" windowWidth="28800" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9020" yWindow="9260" windowWidth="28800" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>##var</t>
   </si>
@@ -103,15 +103,34 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>item.TbReward</t>
+    <t>TbGameSceneData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>reward.xlsx</t>
+    <t>GameSceneData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>item.Reward</t>
+    <t>GameSceneData.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>游戏场景配置</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbCharacterData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterData.xlsx</t>
+  </si>
+  <si>
+    <t>游戏角色配置</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -137,6 +156,8 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -471,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -581,13 +602,33 @@
         <v>27</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7455A8C-3AB8-4CAA-A390-DDE235D81E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C0CED1-EF3F-4B17-BEC6-7F0B425553F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9020" yWindow="9260" windowWidth="28800" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="4965" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -103,34 +103,33 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
-    <t>TbGameSceneData</t>
+    <t>TbDialogueData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>GameSceneData</t>
+    <t>DialogueData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>GameSceneData.xlsx</t>
+    <t>DialogueData.xlsx</t>
+  </si>
+  <si>
+    <t>游戏对话配置数据</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>游戏场景配置</t>
+    <t>NpcData.xlsx</t>
+  </si>
+  <si>
+    <t>TbNpcData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TbCharacterData</t>
+    <t>NpcData</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CharacterData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterData.xlsx</t>
-  </si>
-  <si>
-    <t>游戏角色配置</t>
+    <t>NPC配置表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -616,16 +615,16 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>33</v>
+      <c r="E5" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>34</v>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53C0CED1-EF3F-4B17-BEC6-7F0B425553F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8FA6D0-76E6-4E16-9C39-23D1416DA9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="4965" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15030" yWindow="1820" windowWidth="24520" windowHeight="10250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -130,6 +130,21 @@
   </si>
   <si>
     <t>NPC配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbClothShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClothShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClothShopData.xlsx</t>
+  </si>
+  <si>
+    <t>布料商店配置表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -491,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -630,6 +645,23 @@
         <v>34</v>
       </c>
     </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8FA6D0-76E6-4E16-9C39-23D1416DA9B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D91406-2DD4-415A-879D-E903FB9D4546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15030" yWindow="1820" windowWidth="24520" windowHeight="10250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="25740" windowHeight="10250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
   <si>
     <t>##var</t>
   </si>
@@ -145,6 +145,36 @@
   </si>
   <si>
     <t>布料商店配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbPropertyData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropertyData.xlsx</t>
+  </si>
+  <si>
+    <t>PropertyData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbUIPageData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIPageData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UIPageData.xlsx</t>
+  </si>
+  <si>
+    <t>UI界面配置表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -506,7 +536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -662,6 +692,40 @@
         <v>38</v>
       </c>
     </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D91406-2DD4-415A-879D-E903FB9D4546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022C5851-0C67-4434-BED9-B2D21940F4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="25740" windowHeight="10250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="60450" yWindow="6825" windowWidth="38610" windowHeight="16155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -175,6 +175,36 @@
   </si>
   <si>
     <t>UI界面配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbCharacterData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterData.xlsx</t>
+  </si>
+  <si>
+    <t>TbCharacterShowRuleData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterShowRuleData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterShowRuleData.xlsx</t>
+  </si>
+  <si>
+    <t>角色配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色场景配置表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -244,7 +274,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -259,6 +289,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -536,12 +572,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="20.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.58203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="32.58203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="2" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" style="2" customWidth="1"/>
     <col min="5" max="5" width="24.33203125" style="2" customWidth="1"/>
     <col min="6" max="8" width="18" style="2" customWidth="1"/>
@@ -555,7 +591,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -590,7 +626,7 @@
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -622,6 +658,7 @@
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="B3" s="5"/>
       <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
@@ -676,7 +713,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -693,7 +730,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="4" t="s">
@@ -710,7 +747,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C8" s="4" t="s">
@@ -724,6 +761,40 @@
       </c>
       <c r="I8" s="4" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022C5851-0C67-4434-BED9-B2D21940F4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35603F13-6A56-4BA6-B42C-FE936644FA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60450" yWindow="6825" windowWidth="38610" windowHeight="16155" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="4840" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -205,6 +205,21 @@
   </si>
   <si>
     <t>角色场景配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperMarketShopData.xlsx</t>
+  </si>
+  <si>
+    <t>TbSuperMarketShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperMarketShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超市商店数据</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -243,7 +258,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -253,6 +268,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -274,7 +295,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -295,6 +316,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -572,7 +602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -712,20 +742,20 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="3" t="s">
+    <row r="6" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2" t="b">
+      <c r="D6" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -795,6 +825,23 @@
       </c>
       <c r="I10" s="4" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35603F13-6A56-4BA6-B42C-FE936644FA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EF3861-874B-4C23-AB2A-FEAA84F64A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="4840" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6270" yWindow="2950" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -189,22 +189,7 @@
     <t>CharacterData.xlsx</t>
   </si>
   <si>
-    <t>TbCharacterShowRuleData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterShowRuleData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterShowRuleData.xlsx</t>
-  </si>
-  <si>
     <t>角色配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>角色场景配置表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -602,7 +587,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -807,41 +792,24 @@
         <v>49</v>
       </c>
       <c r="I9" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="9" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58EF3861-874B-4C23-AB2A-FEAA84F64A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4A9A43-6F0A-495A-A05A-5539B8485789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6270" yWindow="2950" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12030" yWindow="3960" windowWidth="38610" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -193,18 +193,35 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>TbSuperMarketShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperMarketShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>超市商店数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbGameSceneData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameSceneData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>SuperMarketShopData.xlsx</t>
-  </si>
-  <si>
-    <t>TbSuperMarketShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperMarketShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>超市商店数据</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GameSceneData.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景配置表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -587,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -797,19 +814,36 @@
     </row>
     <row r="10" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>53</v>
       </c>
       <c r="D10" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>51</v>
+      <c r="E10" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="I10" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="3" t="s">
         <v>54</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD4A9A43-6F0A-495A-A05A-5539B8485789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E4BF9E-31F0-4825-B531-21C309B200EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12030" yWindow="3960" windowWidth="38610" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1970" yWindow="7300" windowWidth="40970" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -222,6 +222,22 @@
   </si>
   <si>
     <t>场景配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbWordMapSceneData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordMapSceneData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>WordMapSceneData.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>世界地图配置表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -604,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -846,6 +862,23 @@
         <v>58</v>
       </c>
     </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E4BF9E-31F0-4825-B531-21C309B200EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17D5AB6-5059-4661-AABE-47EA147170DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1970" yWindow="7300" windowWidth="40970" windowHeight="15960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12350" yWindow="6600" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
   <si>
     <t>##var</t>
   </si>
@@ -238,6 +238,36 @@
   </si>
   <si>
     <t>世界地图配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FruitShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbFruitShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FruitShopData.xlsx</t>
+  </si>
+  <si>
+    <t>果蔬店配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbSexToShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SexToShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SexToyStoreData.xlsx</t>
+  </si>
+  <si>
+    <t>情趣用品店配置表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -620,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -879,6 +909,40 @@
         <v>62</v>
       </c>
     </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A17D5AB6-5059-4661-AABE-47EA147170DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712CEECE-3BFA-4E2E-8F3C-80BFE1B913D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12350" yWindow="6600" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18530" yWindow="7990" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712CEECE-3BFA-4E2E-8F3C-80BFE1B913D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF45558-2F39-4848-99CF-EE52DD525DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-18530" yWindow="7990" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11920" yWindow="4050" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>##var</t>
   </si>
@@ -268,6 +268,21 @@
   </si>
   <si>
     <t>情趣用品店配置表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbFishShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FishShopData.xlsx</t>
+  </si>
+  <si>
+    <t>FishShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钓鱼商店</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -650,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -943,6 +958,23 @@
         <v>70</v>
       </c>
     </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EF45558-2F39-4848-99CF-EE52DD525DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C311ED1-CB9A-4334-A93F-CE613225655E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11920" yWindow="4050" windowWidth="42470" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5440" yWindow="3390" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
   <si>
     <t>##var</t>
   </si>
@@ -275,14 +275,30 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>FishShopData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>钓鱼商店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbUnlockConditionsData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockConditionsData</t>
+  </si>
+  <si>
     <t>FishShopData.xlsx</t>
-  </si>
-  <si>
-    <t>FishShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>钓鱼商店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>UnlockConditionsData.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>解锁条件表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -665,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -963,16 +979,33 @@
         <v>71</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="D15" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I15" s="4" t="s">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="3" t="s">
         <v>74</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C311ED1-CB9A-4334-A93F-CE613225655E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD1EA20-3F30-4832-AF84-D614630CA144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5440" yWindow="3390" windowWidth="42470" windowHeight="19850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="87">
   <si>
     <t>##var</t>
   </si>
@@ -299,6 +299,35 @@
   </si>
   <si>
     <t>解锁条件表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NpcSpawnRuleData.xlsx</t>
+  </si>
+  <si>
+    <t>TbNpcSpawnRuleData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NpcSpawnRuleData</t>
+  </si>
+  <si>
+    <t>NPC随机表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbNpcSpawnGroupData</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>NpcSpawnGroupData</t>
+  </si>
+  <si>
+    <t>NpcSpawnGroupData.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>场景随机出厂时刻表</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -681,7 +710,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1008,6 +1037,40 @@
         <v>78</v>
       </c>
     </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCD1EA20-3F30-4832-AF84-D614630CA144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -104,238 +111,196 @@
   </si>
   <si>
     <t>TbDialogueData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>DialogueData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>DialogueData.xlsx</t>
   </si>
   <si>
     <t>游戏对话配置数据</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbNpcData</t>
+  </si>
+  <si>
+    <t>NpcData</t>
   </si>
   <si>
     <t>NpcData.xlsx</t>
   </si>
   <si>
-    <t>TbNpcData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NpcData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>NPC配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbClothShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ClothShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>ClothShopData.xlsx</t>
   </si>
   <si>
     <t>布料商店配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbPropertyData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PropertyData</t>
   </si>
   <si>
     <t>PropertyData.xlsx</t>
   </si>
   <si>
-    <t>PropertyData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>属性配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbUIPageData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>UIPageData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>UIPageData.xlsx</t>
   </si>
   <si>
     <t>UI界面配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbCharacterData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>CharacterData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>CharacterData.xlsx</t>
   </si>
   <si>
     <t>角色配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbSuperMarketShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>SuperMarketShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SuperMarketShopData.xlsx</t>
   </si>
   <si>
     <t>超市商店数据</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbGameSceneData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>GameSceneData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SuperMarketShopData.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>GameSceneData.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>场景配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbWordMapSceneData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>WordMapSceneData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>WordMapSceneData.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>世界地图配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbFruitShopData</t>
   </si>
   <si>
     <t>FruitShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbFruitShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>FruitShopData.xlsx</t>
   </si>
   <si>
     <t>果蔬店配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbSexToShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>SexToShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>SexToyStoreData.xlsx</t>
   </si>
   <si>
     <t>情趣用品店配置表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbFishShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>FishShopData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FishShopData.xlsx</t>
   </si>
   <si>
     <t>钓鱼商店</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbUnlockConditionsData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>UnlockConditionsData</t>
   </si>
   <si>
-    <t>FishShopData.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>UnlockConditionsData.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>解锁条件表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbNpcSpawnRuleData</t>
+  </si>
+  <si>
+    <t>NpcSpawnRuleData</t>
   </si>
   <si>
     <t>NpcSpawnRuleData.xlsx</t>
   </si>
   <si>
-    <t>TbNpcSpawnRuleData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>NpcSpawnRuleData</t>
-  </si>
-  <si>
     <t>NPC随机表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>TbNpcSpawnGroupData</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>NpcSpawnGroupData</t>
   </si>
   <si>
     <t>NpcSpawnGroupData.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>场景随机出厂时刻表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,13 +312,6 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -361,12 +319,148 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -381,12 +475,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -394,12 +668,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -407,46 +920,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -704,28 +1260,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="32.58203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="26.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" style="2" customWidth="1"/>
-    <col min="6" max="8" width="18" style="2" customWidth="1"/>
-    <col min="9" max="9" width="28.08203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="22.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="24.5" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="32.5833333333333" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="32.3333333333333" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.3333333333333" style="3" customWidth="1"/>
+    <col min="6" max="8" width="18" style="3" customWidth="1"/>
+    <col min="9" max="9" width="28.0833333333333" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="24.5" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,7 +1316,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" s="1" customFormat="1" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -792,7 +1348,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="70" x14ac:dyDescent="0.3">
+    <row r="3" s="1" customFormat="1" ht="70" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -816,264 +1372,264 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="3" t="s">
+    <row r="4" spans="1:11">
+      <c r="B4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="2" t="b">
+      <c r="D4" s="3" t="b">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="3" t="s">
+    <row r="5" spans="1:11">
+      <c r="B5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" s="2" customFormat="1" spans="1:11">
       <c r="B6" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="7" t="b">
+      <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="2" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="9" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="3" t="s">
+    <row r="7" spans="1:11">
+      <c r="B7" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="2" t="b">
+      <c r="I7" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="B8" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="b">
+      <c r="E8" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="B9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" s="2" customFormat="1" spans="1:11">
       <c r="B10" s="8" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="7" t="b">
+      <c r="D10" s="2" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I10" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="7" t="b">
+      <c r="D11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
+    <row r="12" spans="1:11">
+      <c r="B12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="2" t="b">
+      <c r="D12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="3" t="s">
+    <row r="13" spans="1:11">
+      <c r="B13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D13" s="2" t="b">
+      <c r="D13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:11">
+      <c r="B14" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="2" t="b">
+      <c r="D14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:11">
+      <c r="B15" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="2" t="b">
+      <c r="D15" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I15" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D16" s="2" t="b">
+      <c r="D16" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="2:9">
+      <c r="B17" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="2" t="b">
+      <c r="I17" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="7" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EEFE2F-EDB8-45A0-B309-267634C91324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="11470" yWindow="1120" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -288,19 +294,29 @@
   </si>
   <si>
     <t>场景随机出厂时刻表</t>
+  </si>
+  <si>
+    <t>TbDollCatalogData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DollCatalogData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DollCatalogData.xlsx</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>娃娃机配置</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,155 +328,29 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -475,192 +365,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39994506668294322"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -668,259 +378,20 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -932,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -947,62 +418,25 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1260,28 +694,28 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="32.5833333333333" style="4" customWidth="1"/>
+    <col min="2" max="2" width="32.58203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.3333333333333" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.3333333333333" style="3" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="24.33203125" style="3" customWidth="1"/>
     <col min="6" max="8" width="18" style="3" customWidth="1"/>
-    <col min="9" max="9" width="28.0833333333333" style="3" customWidth="1"/>
+    <col min="9" max="9" width="28.08203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="22.5" style="3" customWidth="1"/>
     <col min="11" max="11" width="24.5" style="3" customWidth="1"/>
     <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1316,7 +750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -1348,7 +782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="70" spans="1:11">
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="70" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1372,7 +806,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="6" t="s">
         <v>27</v>
       </c>
@@ -1389,7 +823,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="6" t="s">
         <v>31</v>
       </c>
@@ -1406,7 +840,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:11">
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B6" s="8" t="s">
         <v>35</v>
       </c>
@@ -1423,7 +857,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>39</v>
       </c>
@@ -1440,7 +874,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="6" t="s">
         <v>43</v>
       </c>
@@ -1457,7 +891,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="6" t="s">
         <v>47</v>
       </c>
@@ -1474,7 +908,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" spans="1:11">
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B10" s="8" t="s">
         <v>51</v>
       </c>
@@ -1491,7 +925,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="6" t="s">
         <v>55</v>
       </c>
@@ -1508,7 +942,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="6" t="s">
         <v>59</v>
       </c>
@@ -1525,7 +959,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="6" t="s">
         <v>63</v>
       </c>
@@ -1542,7 +976,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="6" t="s">
         <v>67</v>
       </c>
@@ -1559,7 +993,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="6" t="s">
         <v>71</v>
       </c>
@@ -1576,7 +1010,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="6" t="s">
         <v>75</v>
       </c>
@@ -1593,7 +1027,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17" s="6" t="s">
         <v>79</v>
       </c>
@@ -1610,7 +1044,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="6" t="s">
         <v>83</v>
       </c>
@@ -1627,9 +1061,26 @@
         <v>86</v>
       </c>
     </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EEFE2F-EDB8-45A0-B309-267634C91324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68085017-67D5-459B-88E1-53B2089D6577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11470" yWindow="1120" windowWidth="38610" windowHeight="19220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20180" yWindow="2660" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
   <si>
     <t>##var</t>
   </si>
@@ -309,6 +309,18 @@
   </si>
   <si>
     <t>娃娃机配置</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbItemData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemData.xlsx</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -700,7 +712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1078,6 +1090,20 @@
         <v>90</v>
       </c>
     </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -1,39 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68085017-67D5-459B-88E1-53B2089D6577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20180" yWindow="2660" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30220" windowHeight="18660" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="smNativeData">
+      <pm:revision xmlns:pm="smNativeData" day="1783500526" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783500526" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783500526" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783500526"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
   <si>
     <t>##var</t>
   </si>
@@ -297,69 +287,76 @@
   </si>
   <si>
     <t>TbDollCatalogData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>DollCatalogData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>DollCatalogData.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>娃娃机配置</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbItemData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemData.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783500526" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783500526" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783500526" fgClr="006100" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
   <fills count="4">
@@ -372,41 +369,104 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500526" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF8EA9DB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783500526" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500526"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500526"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783500526"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -415,47 +475,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="1" builtinId="26" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="smNativeData">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783500526" count="1">
+        <pm:charStyle name="普通" fontId="0" Id="1"/>
+      </pm:charStyles>
+      <pm:colors xmlns:pm="smNativeData" id="1783500526" count="4">
+        <pm:color name="颜色 24" rgb="006100"/>
+        <pm:color name="颜色 25" rgb="C6EFCE"/>
+        <pm:color name="20% 灰色" rgb="000000"/>
+        <pm:color name="颜色 27" rgb="8EA9DB"/>
+      </pm:colors>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -465,106 +523,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="EEECE1"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="1F497D"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="等线"/>
+        <a:ea typeface="SimSun"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -576,537 +574,610 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr>
+        <a:prstTxWarp prst="textNoShape">
+          <a:avLst/>
+        </a:prstTxWarp>
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr>
+          <a:defRPr/>
+        </a:defPPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <dimension ref="A1:K20"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="32.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" style="3" customWidth="1"/>
-    <col min="6" max="8" width="18" style="3" customWidth="1"/>
-    <col min="9" max="9" width="28.08203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="24.5" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9.000000" style="4"/>
+    <col min="2" max="2" width="32.577586" customWidth="1" style="5"/>
+    <col min="3" max="3" width="26.750000" customWidth="1" style="4"/>
+    <col min="4" max="4" width="32.327586" customWidth="1" style="4"/>
+    <col min="5" max="5" width="24.327586" customWidth="1" style="4"/>
+    <col min="6" max="8" width="18.000000" customWidth="1" style="4"/>
+    <col min="9" max="9" width="28.077586" customWidth="1" style="4"/>
+    <col min="10" max="10" width="22.500000" customWidth="1" style="4"/>
+    <col min="11" max="11" width="24.500000" customWidth="1" style="4"/>
+    <col min="12" max="16384" width="9.000000" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:11" s="2" customFormat="1">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="70" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:11" s="2" customFormat="1">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="6"/>
+      <c r="D3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="2:9">
+      <c r="B4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="1" t="s">
+      <c r="D4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="2:9">
+      <c r="B5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="D5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="8" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
+    <row r="6" spans="2:9" s="3" customFormat="1">
+      <c r="B6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="D6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="10" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+    <row r="7" spans="2:9">
+      <c r="B7" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="D7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+    <row r="8" spans="2:9">
+      <c r="B8" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7" t="s">
+      <c r="D8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="8" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="2:9">
+      <c r="B9" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
+      <c r="D9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
+    <row r="10" spans="2:9" s="3" customFormat="1">
+      <c r="B10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9" t="s">
+      <c r="D10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="10" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="2:9">
+      <c r="B11" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="7" t="s">
+      <c r="D11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="8" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
+    <row r="12" spans="2:9">
+      <c r="B12" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7" t="s">
+      <c r="D12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="8" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="2:9">
+      <c r="B13" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3" t="s">
+      <c r="D13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="8" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="6" t="s">
+    <row r="14" spans="2:9">
+      <c r="B14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="8" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="6" t="s">
+    <row r="15" spans="2:9">
+      <c r="B15" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="6" t="s">
+    <row r="16" spans="2:9">
+      <c r="B16" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7" t="s">
+      <c r="D16" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="8" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="6" t="s">
+    <row r="17" spans="2:9">
+      <c r="B17" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="D17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="8" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="6" t="s">
+    <row r="18" spans="2:9">
+      <c r="B18" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="8" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="10" t="s">
+    <row r="19" spans="2:9">
+      <c r="B19" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="11" t="s">
+      <c r="D19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="8" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>93</v>
-      </c>
+    <row r="20" spans="2:5">
+      <c r="B20" s="7"/>
+      <c r="C20" s="8"/>
+      <c r="E20" s="8"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783500526" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783500526" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783500526" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783500526" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783500526" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783500526" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68085017-67D5-459B-88E1-53B2089D6577}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7E1213-2479-4517-AA0C-517ABA587338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20180" yWindow="2660" windowWidth="30220" windowHeight="18660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9660" yWindow="760" windowWidth="28220" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
   <si>
     <t>##var</t>
   </si>
@@ -320,7 +320,24 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>ItemData.xlsx</t>
+    <t xml:space="preserve"> TbConsumablesItemData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ConsumablesItemData</t>
+  </si>
+  <si>
+    <t>MaterialItemData@ItemData.xlsx</t>
+  </si>
+  <si>
+    <t>ConsumablesItemData@ItemData.xlsx</t>
+  </si>
+  <si>
+    <t>材料道具配置表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗品道具配置表</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -340,17 +357,23 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -399,7 +422,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -435,6 +458,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -712,14 +741,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="32.58203125" style="4" customWidth="1"/>
     <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="24.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" style="4" customWidth="1"/>
     <col min="6" max="8" width="18" style="3" customWidth="1"/>
     <col min="9" max="9" width="28.08203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="22.5" style="3" customWidth="1"/>
@@ -740,7 +769,7 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -775,7 +804,7 @@
       <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -802,7 +831,7 @@
       <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -828,7 +857,7 @@
       <c r="D4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="7" t="s">
@@ -845,7 +874,7 @@
       <c r="D5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="I5" s="7" t="s">
@@ -862,7 +891,7 @@
       <c r="D6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="13" t="s">
         <v>37</v>
       </c>
       <c r="I6" s="9" t="s">
@@ -879,7 +908,7 @@
       <c r="D7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>41</v>
       </c>
       <c r="I7" s="7" t="s">
@@ -896,7 +925,7 @@
       <c r="D8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>45</v>
       </c>
       <c r="I8" s="7" t="s">
@@ -913,7 +942,7 @@
       <c r="D9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>49</v>
       </c>
       <c r="I9" s="7" t="s">
@@ -930,7 +959,7 @@
       <c r="D10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="8" t="s">
         <v>53</v>
       </c>
       <c r="I10" s="9" t="s">
@@ -947,7 +976,7 @@
       <c r="D11" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>57</v>
       </c>
       <c r="I11" s="7" t="s">
@@ -964,7 +993,7 @@
       <c r="D12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>61</v>
       </c>
       <c r="I12" s="7" t="s">
@@ -981,7 +1010,7 @@
       <c r="D13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="4" t="s">
         <v>65</v>
       </c>
       <c r="I13" s="7" t="s">
@@ -998,7 +1027,7 @@
       <c r="D14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="E14" s="4" t="s">
         <v>69</v>
       </c>
       <c r="I14" s="7" t="s">
@@ -1015,7 +1044,7 @@
       <c r="D15" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>73</v>
       </c>
       <c r="I15" s="7" t="s">
@@ -1032,7 +1061,7 @@
       <c r="D16" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>77</v>
       </c>
       <c r="I16" s="7" t="s">
@@ -1049,7 +1078,7 @@
       <c r="D17" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="E17" s="4" t="s">
         <v>81</v>
       </c>
       <c r="I17" s="7" t="s">
@@ -1066,7 +1095,7 @@
       <c r="D18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>85</v>
       </c>
       <c r="I18" s="7" t="s">
@@ -1083,7 +1112,7 @@
       <c r="D19" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="E19" s="10" t="s">
         <v>89</v>
       </c>
       <c r="I19" s="11" t="s">
@@ -1091,17 +1120,37 @@
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="7" t="s">
         <v>92</v>
       </c>
       <c r="D20" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="12" t="s">
         <v>93</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7E1213-2479-4517-AA0C-517ABA587338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2A5497-03E1-43CC-969B-3A5A16693884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9660" yWindow="760" windowWidth="28220" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5610" yWindow="2070" windowWidth="30580" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
   <si>
     <t>##var</t>
   </si>
@@ -338,6 +338,18 @@
   </si>
   <si>
     <t>消耗品道具配置表</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> TbRecipeItemData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecipeItemData</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>RecipeItemData@ItemData.xlsx</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -345,7 +357,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -384,6 +396,13 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -414,15 +433,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -465,9 +487,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="2" builtinId="8"/>
     <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -741,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1153,8 +1179,28 @@
         <v>98</v>
       </c>
     </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E22" r:id="rId1" xr:uid="{4AB6DBF6-B686-407A-959B-050E46E28A9F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -1,39 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
+  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2A5497-03E1-43CC-969B-3A5A16693884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5610" yWindow="2070" windowWidth="30580" windowHeight="18810" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30580" windowHeight="18810" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="smNativeData">
+      <pm:revision xmlns:pm="smNativeData" day="1783652861" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
+      <pm:docPrefs xmlns:pm="smNativeData" id="1783652861" fixedDigits="0" showNotice="1" showFrameBounds="1" autoChart="1" recalcOnPrint="1" recalcOnCopy="1" finalRounding="1" compatTextArt="1" tab="567" useDefinedPrintRange="1" printArea="currentSheet"/>
+      <pm:compatibility xmlns:pm="smNativeData" id="1783652861" overlapCells="1"/>
+      <pm:defCurrency xmlns:pm="smNativeData" id="1783652861"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
   <si>
     <t>##var</t>
   </si>
@@ -297,114 +287,174 @@
   </si>
   <si>
     <t>TbDollCatalogData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>DollCatalogData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>DollCatalogData.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>娃娃机配置</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>TbItemData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>ItemData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemData@ItemData.xlsx</t>
+  </si>
+  <si>
+    <t>道具配置表</t>
   </si>
   <si>
     <t xml:space="preserve"> TbConsumablesItemData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>ConsumablesItemData</t>
   </si>
   <si>
+    <t>ConsumablesItemData@ItemData.xlsx</t>
+  </si>
+  <si>
+    <t>消耗品道具配置表</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TbRecipeItemData</t>
+  </si>
+  <si>
+    <t>RecipeItemData</t>
+  </si>
+  <si>
+    <t>RecipeItemData@ItemData.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TbMaterialItemData</t>
+  </si>
+  <si>
+    <t>MaterialItemData</t>
+  </si>
+  <si>
     <t>MaterialItemData@ItemData.xlsx</t>
   </si>
   <si>
-    <t>ConsumablesItemData@ItemData.xlsx</t>
-  </si>
-  <si>
     <t>材料道具配置表</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>消耗品道具配置表</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> TbRecipeItemData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RecipeItemData</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>RecipeItemData@ItemData.xlsx</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="8">
+    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
+    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
+    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
+  </numFmts>
+  <fonts count="6">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" ulstyle="none" kern="1">
+            <pm:latin face="Arial" sz="200" lang="default"/>
+            <pm:cs face="Times New Roman" sz="200" lang="default"/>
+            <pm:ea face="SimSun" sz="200" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF006100"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" fgClr="006100" ulstyle="none" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+      <color rgb="FF0563C1"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" fgClr="0563C1" ulstyle="single" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF0563C1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" fgClr="0563C1" ulstyle="single" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+            <hyperlink type="3" url="mailto:RecipeItemData@ItemData.xlsx" location="" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
     <font>
-      <u/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF0563C1"/>
       <sz val="11"/>
-      <color theme="10"/>
-      <name val="等线"/>
-      <scheme val="minor"/>
+      <u val="single"/>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" fgClr="0563C1" ulstyle="single" kern="1">
+            <pm:latin face="等线" sz="220" lang="default"/>
+            <pm:cs face="Times New Roman" sz="220" lang="default"/>
+            <pm:ea face="SimSun" sz="220" lang="default"/>
+            <hyperlink type="3" url="mailto:MaterialItemData@ItemData.xlsx" location="" text=""/>
+          </pm:charSpec>
+        </ext>
+      </extLst>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -414,44 +464,140 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783652861" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39994506668294322"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF8EA9DB"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783652861" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00000000"/>
+          </ext>
+        </extLst>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+        <extLst>
+          <ext uri="smNativeData">
+            <pm:shade xmlns:pm="smNativeData" id="1783652861" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
+          </ext>
+        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783652861"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783652861"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783652861"/>
+        </ext>
+      </extLst>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="none">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="none">
+        <color rgb="FF000000"/>
+      </bottom>
+      <extLst>
+        <ext uri="smNativeData">
+          <pm:border xmlns:pm="smNativeData" id="1783652861"/>
+        </ext>
+      </extLst>
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -460,57 +606,62 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="2" builtinId="8"/>
-    <cellStyle name="好" xfId="1" builtinId="26"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="1" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="smNativeData">
+      <pm:charStyles xmlns:pm="smNativeData" id="1783652861" count="1">
+        <pm:charStyle name="普通" fontId="0" Id="1"/>
+      </pm:charStyles>
+      <pm:colors xmlns:pm="smNativeData" id="1783652861" count="5">
+        <pm:color name="颜色 24" rgb="006100"/>
+        <pm:color name="颜色 25" rgb="0563C1"/>
+        <pm:color name="颜色 26" rgb="C6EFCE"/>
+        <pm:color name="20% 灰色" rgb="000000"/>
+        <pm:color name="颜色 28" rgb="8EA9DB"/>
+      </pm:colors>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -520,106 +671,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="EEECE1"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="1F497D"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="等线"/>
+        <a:ea typeface="SimSun"/>
+        <a:cs typeface="Times New Roman"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -631,577 +722,678 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr>
+        <a:prstTxWarp prst="textNoShape">
+          <a:avLst/>
+        </a:prstTxWarp>
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr>
+          <a:defRPr/>
+        </a:defPPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <dimension ref="A1:K23"/>
+  <sheetFormatPr defaultRowHeight="13.45"/>
   <cols>
-    <col min="1" max="1" width="9" style="3"/>
-    <col min="2" max="2" width="32.58203125" style="4" customWidth="1"/>
-    <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="32.33203125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="36.1640625" style="4" customWidth="1"/>
-    <col min="6" max="8" width="18" style="3" customWidth="1"/>
-    <col min="9" max="9" width="28.08203125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="22.5" style="3" customWidth="1"/>
-    <col min="11" max="11" width="24.5" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="9.000000" style="5"/>
+    <col min="2" max="2" width="32.577586" customWidth="1" style="6"/>
+    <col min="3" max="3" width="26.750000" customWidth="1" style="5"/>
+    <col min="4" max="4" width="32.327586" customWidth="1" style="5"/>
+    <col min="5" max="5" width="36.163793" customWidth="1" style="6"/>
+    <col min="6" max="8" width="18.000000" customWidth="1" style="5"/>
+    <col min="9" max="9" width="28.077586" customWidth="1" style="5"/>
+    <col min="10" max="10" width="22.500000" customWidth="1" style="5"/>
+    <col min="11" max="11" width="24.500000" customWidth="1" style="5"/>
+    <col min="12" max="16384" width="9.000000" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:11" s="3" customFormat="1">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:11" s="3" customFormat="1">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="70" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:11" s="3" customFormat="1">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="D3" s="1" t="s">
+      <c r="B3" s="7"/>
+      <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="2:9">
+      <c r="B4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="2:9">
+      <c r="B5" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="9" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
+    <row r="6" spans="2:9" s="4" customFormat="1">
+      <c r="B6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2" t="b">
+      <c r="D6" s="4" t="b">
         <v>1</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="11" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
+    <row r="7" spans="2:9">
+      <c r="B7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="D7" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="6" t="s">
+    <row r="8" spans="2:9">
+      <c r="B8" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="2:9">
+      <c r="B9" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="9" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="8" t="s">
+    <row r="10" spans="2:9" s="4" customFormat="1">
+      <c r="B10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="D10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="9" t="s">
+      <c r="I10" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="2:9">
+      <c r="B11" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="9" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="6" t="s">
+    <row r="12" spans="2:9">
+      <c r="B12" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="2:9">
+      <c r="B13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="4" t="s">
+      <c r="D13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="6" t="s">
+    <row r="14" spans="2:9">
+      <c r="B14" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="D14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="9" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="6" t="s">
+    <row r="15" spans="2:9">
+      <c r="B15" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="9" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="6" t="s">
+    <row r="16" spans="2:9">
+      <c r="B16" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="9" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="6" t="s">
+    <row r="17" spans="2:9">
+      <c r="B17" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="D17" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="9" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="6" t="s">
+    <row r="18" spans="2:9">
+      <c r="B18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="I18" s="7" t="s">
+      <c r="I18" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="10" t="s">
+    <row r="19" spans="2:9">
+      <c r="B19" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="10" t="s">
+      <c r="D19" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="I19" s="11" t="s">
+      <c r="I19" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="6" t="s">
+    <row r="20" spans="2:9">
+      <c r="B20" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="12" t="s">
+      <c r="D20" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="I20" s="7" t="s">
+      <c r="C21" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="12" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:9">
       <c r="B22" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="3" t="b">
+      <c r="D22" s="5" t="b">
         <v>1</v>
       </c>
       <c r="E22" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="I22" s="7" t="s">
+      <c r="I22" s="9" t="s">
         <v>98</v>
       </c>
     </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E22" r:id="rId1" xr:uid="{4AB6DBF6-B686-407A-959B-050E46E28A9F}"/>
+    <hyperlink ref="E20" r:id="rId1"/>
+    <hyperlink ref="E22" r:id="rId2"/>
+    <hyperlink ref="E23" r:id="rId1"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <printOptions>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:pageFlags xmlns:pm="smNativeData" id="1783652861" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
+      </ext>
+    </extLst>
+  </printOptions>
+  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
+  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
+  <headerFooter>
+    <extLst>
+      <ext uri="smNativeData">
+        <pm:header xmlns:pm="smNativeData" id="1783652861" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
+        <pm:footer xmlns:pm="smNativeData" id="1783652861" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783652861" Id="0" type="0" value="0"/>
+        <pm:paperBin xmlns:pm="smNativeData" id="1783652861" Id="1" type="0" value="0"/>
+      </ext>
+    </extLst>
+  </headerFooter>
+  <extLst>
+    <ext uri="smNativeData">
+      <pm:sheetPrefs xmlns:pm="smNativeData" day="1783652861" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">
+        <pm:shade id="0" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+        <pm:shade id="1" type="0" fgLvl="100" fgClr="000000" bgLvl="100" bgClr="FFFFFF"/>
+      </pm:sheetPrefs>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D16DDDB-AE1D-458E-9C84-4213C86A3A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="30580" windowHeight="18810" tabRatio="500"/>
+    <workbookView xWindow="2280" yWindow="2200" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1783652861" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -331,130 +336,70 @@
     <t>RecipeItemData@ItemData.xlsx</t>
   </si>
   <si>
+    <t>材料道具配置表</t>
+  </si>
+  <si>
     <t xml:space="preserve"> TbMaterialItemData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MaterialItemData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>MaterialItemData@ItemData.xlsx</t>
-  </si>
-  <si>
-    <t>材料道具配置表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-  </numFmts>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" fgClr="006100" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" fgClr="0563C1" ulstyle="single" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" fgClr="0563C1" ulstyle="single" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-            <hyperlink type="3" url="mailto:RecipeItemData@ItemData.xlsx" location="" text=""/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
-      <color rgb="FF0563C1"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1783652861" fgClr="0563C1" ulstyle="single" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-            <hyperlink type="3" url="mailto:MaterialItemData@ItemData.xlsx" location="" text=""/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -465,139 +410,57 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652861" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8EA9DB"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652861" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00000000"/>
-          </ext>
-        </extLst>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1783652861" type="1" fgLvl="100" fgClr="00FFFFFF" bgLvl="100" bgClr="00000000"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652861"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652861"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652861"/>
-        </ext>
-      </extLst>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1783652861"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -606,44 +469,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="1" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="超链接" xfId="2" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="好" xfId="1" builtinId="26" customBuiltin="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1783652861" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -915,478 +779,462 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K23"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.000000" style="5"/>
-    <col min="2" max="2" width="32.577586" customWidth="1" style="6"/>
-    <col min="3" max="3" width="26.750000" customWidth="1" style="5"/>
-    <col min="4" max="4" width="32.327586" customWidth="1" style="5"/>
-    <col min="5" max="5" width="36.163793" customWidth="1" style="6"/>
-    <col min="6" max="8" width="18.000000" customWidth="1" style="5"/>
-    <col min="9" max="9" width="28.077586" customWidth="1" style="5"/>
-    <col min="10" max="10" width="22.500000" customWidth="1" style="5"/>
-    <col min="11" max="11" width="24.500000" customWidth="1" style="5"/>
-    <col min="12" max="16384" width="9.000000" style="5"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="32.58203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" style="4" customWidth="1"/>
+    <col min="6" max="8" width="18" style="3" customWidth="1"/>
+    <col min="9" max="9" width="28.08203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="24.5" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="3" customFormat="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="3" customFormat="1">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="70" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="5"/>
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="8" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="9" t="s">
+      <c r="I4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
-      <c r="B5" s="8" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="2:9" s="4" customFormat="1">
-      <c r="B6" s="10" t="s">
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="13" t="s">
+      <c r="D6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="8" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
-      <c r="B8" s="8" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8" t="s">
+      <c r="D8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
-      <c r="B9" s="8" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:9" s="4" customFormat="1">
-      <c r="B10" s="10" t="s">
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="10" t="s">
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="2:9">
-      <c r="B11" s="8" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="2:9">
-      <c r="B12" s="8" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8" t="s">
+      <c r="D12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="8" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
-      <c r="B14" s="8" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
-      <c r="B15" s="8" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="D15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="8" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="8" t="s">
+      <c r="D16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="8" t="s">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="8" t="s">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8" t="s">
+      <c r="D18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="8" t="s">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="9" t="s">
+      <c r="C19" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="8" t="s">
+      <c r="D19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="8" t="s">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15" t="s">
+      <c r="D20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="12" t="s">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="12" t="s">
+      <c r="D21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="12" t="s">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14" t="s">
+      <c r="D22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="I22" s="9" t="s">
+      <c r="I22" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="12" t="s">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>105</v>
-      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E20" r:id="rId1"/>
-    <hyperlink ref="E22" r:id="rId2"/>
-    <hyperlink ref="E23" r:id="rId1"/>
+    <hyperlink ref="E20" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E22" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E23" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1783652861" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1783652861" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1783652861" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783652861" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1783652861" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1783652861" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D16DDDB-AE1D-458E-9C84-4213C86A3A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1748B795-E977-48A7-9BF3-3E7EFFDEC658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2200" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3800" yWindow="2920" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -348,6 +348,21 @@
   </si>
   <si>
     <t>MaterialItemData@ItemData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbChatMessageData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChatMessageData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnLineRandomChatData.xlsx</t>
+  </si>
+  <si>
+    <t>角色消息(伪)配置表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -366,24 +381,32 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -453,7 +476,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -491,6 +514,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -780,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -788,7 +814,8 @@
     <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
     <col min="4" max="4" width="32.33203125" style="3" customWidth="1"/>
     <col min="5" max="5" width="36.1640625" style="4" customWidth="1"/>
-    <col min="6" max="8" width="18" style="3" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" style="3" customWidth="1"/>
+    <col min="7" max="8" width="18" style="3" customWidth="1"/>
     <col min="9" max="9" width="28.08203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="22.5" style="3" customWidth="1"/>
     <col min="11" max="11" width="24.5" style="3" customWidth="1"/>
@@ -1224,6 +1251,23 @@
       </c>
       <c r="I23" s="3" t="s">
         <v>102</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1748B795-E977-48A7-9BF3-3E7EFFDEC658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137E50C4-23BA-4B9D-BFA2-2DD110E61EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3800" yWindow="2920" windowWidth="30580" windowHeight="18680" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="65820" yWindow="6270" windowWidth="30585" windowHeight="18675" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="118">
   <si>
     <t>##var</t>
   </si>
@@ -363,6 +363,35 @@
   </si>
   <si>
     <t>角色消息(伪)配置表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbPriavateMessageData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PriavateMessageData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PriavateMessageData.xlsx</t>
+  </si>
+  <si>
+    <t>私信消息配置表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardData</t>
+  </si>
+  <si>
+    <t>TbRewardData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>RewardData.xlsx</t>
+  </si>
+  <si>
+    <t>奖励表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -806,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -889,7 +918,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="1" customFormat="1" ht="70" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="56" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
@@ -1268,6 +1297,40 @@
       </c>
       <c r="I24" s="11" t="s">
         <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{137E50C4-23BA-4B9D-BFA2-2DD110E61EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125BDCA7-2239-4003-AF6F-2062C1640391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="65820" yWindow="6270" windowWidth="30585" windowHeight="18675" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5020" yWindow="1450" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="122">
   <si>
     <t>##var</t>
   </si>
@@ -388,10 +388,26 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>奖励表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbExhibitionInfoData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExhibitionInfoData</t>
+  </si>
+  <si>
+    <t>ExhibitionInfoData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>RewardData.xlsx</t>
-  </si>
-  <si>
-    <t>奖励表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>展会信息表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -835,7 +851,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1326,11 +1342,28 @@
       <c r="D26" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="I26" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="I26" s="11" t="s">
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B27" s="13" t="s">
         <v>117</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125BDCA7-2239-4003-AF6F-2062C1640391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE3186C-EF36-4F79-8A4C-A7032818F177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5020" yWindow="1450" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
   <si>
     <t>##var</t>
   </si>
@@ -408,6 +408,21 @@
   </si>
   <si>
     <t>展会信息表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbPopularityData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PopularityData</t>
+  </si>
+  <si>
+    <t>PopularityData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>展会人气表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -851,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1364,6 +1379,23 @@
       </c>
       <c r="I27" s="11" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B28" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE3186C-EF36-4F79-8A4C-A7032818F177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B39488-5ACD-4EA3-ACF2-AF12D6F65DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="630" yWindow="2500" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -423,6 +423,21 @@
   </si>
   <si>
     <t>展会人气表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbClothingData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClothingData</t>
+  </si>
+  <si>
+    <t>ClothingData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装定义表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -866,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1396,6 +1411,23 @@
       </c>
       <c r="I28" s="11" t="s">
         <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I29" s="11" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B39488-5ACD-4EA3-ACF2-AF12D6F65DC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F891703F-5C78-4210-BDD6-C7FCBA0640C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="2500" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3410" yWindow="2500" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -438,6 +438,21 @@
   </si>
   <si>
     <t>服装定义表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbExhibitionPromotionData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ExhibitionPromotionData</t>
+  </si>
+  <si>
+    <t>ExhibitionPromotionData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>展会宣发表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -881,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1428,6 +1443,23 @@
       </c>
       <c r="I29" s="11" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F891703F-5C78-4210-BDD6-C7FCBA0640C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180512FD-48B0-467F-9A28-1682C916EAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3410" yWindow="2500" windowWidth="30590" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="130">
   <si>
     <t>##var</t>
   </si>
@@ -408,21 +408,6 @@
   </si>
   <si>
     <t>展会信息表</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbPopularityData</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>PopularityData</t>
-  </si>
-  <si>
-    <t>PopularityData.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>展会人气表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -896,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1438,28 +1423,11 @@
       <c r="D29" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E29" s="11" t="s">
         <v>128</v>
       </c>
       <c r="I29" s="11" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D30" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="I30" s="11" t="s">
-        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{180512FD-48B0-467F-9A28-1682C916EAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8724CB-BC59-41F8-8661-3719B30E9BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2500" windowWidth="39220" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="134">
   <si>
     <t>##var</t>
   </si>
@@ -438,6 +438,21 @@
   </si>
   <si>
     <t>展会宣发表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterPropData</t>
+  </si>
+  <si>
+    <t>TbCharacterPropData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CharacterPropData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色属性配置表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -881,7 +896,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1428,6 +1443,23 @@
       </c>
       <c r="I29" s="11" t="s">
         <v>129</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A8724CB-BC59-41F8-8661-3719B30E9BFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62D9742-6C10-471A-B7CB-403A70EE62B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2500" windowWidth="39220" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
   <si>
     <t>##var</t>
   </si>
@@ -454,6 +454,18 @@
   <si>
     <t>角色属性配置表</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbManuscriptItemData</t>
+  </si>
+  <si>
+    <t>ManuscriptItemData</t>
+  </si>
+  <si>
+    <t>ManuscriptItemData@ItemData.xlsx</t>
+  </si>
+  <si>
+    <t>催稿玩法-灵感草稿库配置表</t>
   </si>
 </sst>
 </file>
@@ -566,7 +578,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -608,6 +620,12 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -896,7 +914,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1460,6 +1478,23 @@
       </c>
       <c r="I30" s="11" t="s">
         <v>133</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="I31" s="15" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F62D9742-6C10-471A-B7CB-403A70EE62B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C03D46-0528-4872-9CFC-04A2D33164C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7720" yWindow="4040" windowWidth="26690" windowHeight="12250" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="142">
   <si>
     <t>##var</t>
   </si>
@@ -466,6 +466,22 @@
   </si>
   <si>
     <t>催稿玩法-灵感草稿库配置表</t>
+  </si>
+  <si>
+    <t>TbClothingAccessoriesData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClothingAccessoriesData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ClothingAccessoriesData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装配件定义表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -914,7 +930,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1495,6 +1511,23 @@
       </c>
       <c r="I31" s="15" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B32" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C03D46-0528-4872-9CFC-04A2D33164C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD5BABD-E238-4349-AB52-67B3589592EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7720" yWindow="4040" windowWidth="26690" windowHeight="12250" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="3040" windowWidth="26660" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
   <si>
     <t>##var</t>
   </si>
@@ -481,6 +481,21 @@
   </si>
   <si>
     <t>服装配件定义表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbPcbSlotData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PcbSlotData</t>
+  </si>
+  <si>
+    <t>PcbSlotData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>配件板子定义表</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -930,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1528,6 +1543,23 @@
       </c>
       <c r="I32" s="11" t="s">
         <v>141</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B33" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="11" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD5BABD-E238-4349-AB52-67B3589592EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C4E725-1849-4A30-809F-C0FAAF6A3518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="3040" windowWidth="26660" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="150">
   <si>
     <t>##var</t>
   </si>
@@ -497,6 +497,20 @@
   <si>
     <t>配件板子定义表</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbSprayPaintGameData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>SprayPaintGameData</t>
+  </si>
+  <si>
+    <t>SprayPaintGameData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>服装喷漆小游戏配置</t>
   </si>
 </sst>
 </file>
@@ -945,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1560,6 +1574,23 @@
       </c>
       <c r="I33" s="11" t="s">
         <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B34" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5C4E725-1849-4A30-809F-C0FAAF6A3518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B3EB56-A447-472C-AC2C-7ABE4560B214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="155">
   <si>
     <t>##var</t>
   </si>
@@ -511,6 +511,21 @@
   </si>
   <si>
     <t>服装喷漆小游戏配置</t>
+  </si>
+  <si>
+    <t>TbRacingTrackData</t>
+  </si>
+  <si>
+    <t>RacingTrackData</t>
+  </si>
+  <si>
+    <t>True</t>
+  </si>
+  <si>
+    <t>RacingTrackData.xlsx</t>
+  </si>
+  <si>
+    <t>赛车小游戏赛道配置表</t>
   </si>
 </sst>
 </file>
@@ -959,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1591,6 +1606,23 @@
       </c>
       <c r="I34" s="11" t="s">
         <v>149</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B35" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="I35" s="15" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10B3EB56-A447-472C-AC2C-7ABE4560B214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AB3C16-329C-4393-A0F4-934E5B551D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2500" windowWidth="37150" windowHeight="18380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="159">
   <si>
     <t>##var</t>
   </si>
@@ -526,6 +526,18 @@
   </si>
   <si>
     <t>赛车小游戏赛道配置表</t>
+  </si>
+  <si>
+    <t>TbGiftItemData</t>
+  </si>
+  <si>
+    <t>GiftItemData</t>
+  </si>
+  <si>
+    <t>GiftItemData@ItemData.xlsx</t>
+  </si>
+  <si>
+    <t>礼物道具配置表</t>
   </si>
 </sst>
 </file>
@@ -974,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1623,6 +1635,23 @@
       </c>
       <c r="I35" s="15" t="s">
         <v>154</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B36" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E36" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="I36" s="15" t="s">
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AB3C16-329C-4393-A0F4-934E5B551D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C785D0F5-0B05-4355-9D6C-1447CEBB7DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="167">
   <si>
     <t>##var</t>
   </si>
@@ -538,6 +538,30 @@
   </si>
   <si>
     <t>礼物道具配置表</t>
+  </si>
+  <si>
+    <t>TbQuestStoryCondData</t>
+  </si>
+  <si>
+    <t>QuestStoryCondData</t>
+  </si>
+  <si>
+    <t>QuestStoryCondData.xlsx</t>
+  </si>
+  <si>
+    <t>任务/剧情状态条件表</t>
+  </si>
+  <si>
+    <t>TbQuestData</t>
+  </si>
+  <si>
+    <t>QuestData</t>
+  </si>
+  <si>
+    <t>QuestData.xlsx</t>
+  </si>
+  <si>
+    <t>任务配置表</t>
   </si>
 </sst>
 </file>
@@ -986,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1652,6 +1676,40 @@
       </c>
       <c r="I36" s="15" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B37" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="I37" s="15" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B38" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E38" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="I38" s="15" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C785D0F5-0B05-4355-9D6C-1447CEBB7DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C49150-3F48-4206-8F6E-A1FC1F92FACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -555,13 +555,15 @@
     <t>TbQuestData</t>
   </si>
   <si>
-    <t>QuestData</t>
-  </si>
-  <si>
-    <t>QuestData.xlsx</t>
-  </si>
-  <si>
     <t>任务配置表</t>
+  </si>
+  <si>
+    <t>QuestDataConfig</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>QuestDataConfig.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1700,16 +1702,16 @@
         <v>163</v>
       </c>
       <c r="C38" s="15" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>152</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I38" s="15" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4AB3C16-329C-4393-A0F4-934E5B551D99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF74EB9-F833-4BDD-81D4-D85CF70434F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7930" yWindow="5960" windowWidth="28800" windowHeight="14360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1990" yWindow="1460" windowWidth="37160" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="163">
   <si>
     <t>##var</t>
   </si>
@@ -538,6 +538,21 @@
   </si>
   <si>
     <t>礼物道具配置表</t>
+  </si>
+  <si>
+    <t>DramaBgData</t>
+  </si>
+  <si>
+    <t>TbDramaBgData</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaBgData.xlsx</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧情背景表</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -986,7 +1001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1652,6 +1667,23 @@
       </c>
       <c r="I36" s="15" t="s">
         <v>158</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B37" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06C49150-3F48-4206-8F6E-A1FC1F92FACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81968822-B609-40BB-938E-99C852ECB3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="179">
   <si>
     <t>##var</t>
   </si>
@@ -564,6 +564,42 @@
   <si>
     <t>QuestDataConfig.xlsx</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbQuestObjData</t>
+  </si>
+  <si>
+    <t>QuestObjConfig</t>
+  </si>
+  <si>
+    <t>QuestObjConfig.xlsx</t>
+  </si>
+  <si>
+    <t>任务目标配置表</t>
+  </si>
+  <si>
+    <t>TbQuestCategoryData</t>
+  </si>
+  <si>
+    <t>QuestCategoryData</t>
+  </si>
+  <si>
+    <t>QuestCategoryData.xlsx</t>
+  </si>
+  <si>
+    <t>任务类别配置表</t>
+  </si>
+  <si>
+    <t>TbQuestRewardData</t>
+  </si>
+  <si>
+    <t>QuestRewardData</t>
+  </si>
+  <si>
+    <t>QuestRewardData.xlsx</t>
+  </si>
+  <si>
+    <t>任务奖励展示配置表</t>
   </si>
 </sst>
 </file>
@@ -1012,7 +1048,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1712,6 +1748,57 @@
       </c>
       <c r="I38" s="15" t="s">
         <v>164</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B39" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="I39" s="15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B40" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E40" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I40" s="15" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B41" s="14" t="s">
+        <v>175</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E41" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="I41" s="15" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <fileSharing readOnlyRecommended="0" userName="Lumino Game 03"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C9FAB5-67DE-4389-9661-3E2768470940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0" xWindow="240" yWindow="60" windowWidth="37160" windowHeight="18570" tabRatio="500"/>
+    <workbookView xWindow="4020" yWindow="1330" windowWidth="37160" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:revision xmlns:pm="smNativeData" day="1786418752" val="1234" rev="124" revOS="4" revMin="124" revMax="0"/>
@@ -23,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="187">
   <si>
     <t>##var</t>
   </si>
@@ -572,133 +577,75 @@
   </si>
   <si>
     <t>任务奖励展示配置表</t>
+  </si>
+  <si>
+    <t>TbDramaData</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaData</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaData.xlsx</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧情表</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
-    <numFmt numFmtId="5" formatCode="#,##0\ &quot;¥&quot;;\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="6" formatCode="#,##0\ &quot;¥&quot;;[Red]\-#,##0\ &quot;¥&quot;"/>
-    <numFmt numFmtId="7" formatCode="#,##0.00\ &quot;¥&quot;;\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="8" formatCode="#,##0.00\ &quot;¥&quot;;[Red]\-#,##0.00\ &quot;¥&quot;"/>
-    <numFmt numFmtId="42" formatCode="_-* #,##0\ &quot;¥&quot;_-;\-* #,##0\ &quot;¥&quot;_-;_-* &quot;-&quot;\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0\ _¥_-;\-* #,##0\ _¥_-;_-* &quot;-&quot;\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="44" formatCode="_-* #,##0.00\ &quot;¥&quot;_-;\-* #,##0.00\ &quot;¥&quot;_-;_-* &quot;-&quot;??\ &quot;¥&quot;_-;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00\ _¥_-;\-* #,##0.00\ _¥_-;_-* &quot;-&quot;??\ _¥_-;_-@_-"/>
-    <numFmt numFmtId="49" formatCode="@"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
-      <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1786418752" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1786418752" ulstyle="none" kern="1">
-            <pm:latin face="Arial" sz="200" lang="default"/>
-            <pm:cs face="Times New Roman" sz="200" lang="default"/>
-            <pm:ea face="SimSun" sz="200" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1786418752" fgClr="006100" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1786418752" fgClr="0563C1" ulstyle="single" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1786418752" fgClr="0563C1" ulstyle="single" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-            <hyperlink type="3" url="mailto:MaterialItemData@ItemData.xlsx" location="" text=""/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="等线"/>
-      <charset val="134"/>
-      <color rgb="FF0563C1"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1786418752" fgClr="0563C1" ulstyle="single" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-            <hyperlink type="3" url="mailto:RecipeItemData@ItemData.xlsx" location="" text=""/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
     </font>
     <font>
+      <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <sz val="11"/>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:charSpec xmlns:pm="smNativeData" id="1786418752" fgClr="000000" ulstyle="none" kern="1">
-            <pm:latin face="等线" sz="220" lang="default"/>
-            <pm:cs face="Times New Roman" sz="220" lang="default"/>
-            <pm:ea face="SimSun" sz="220" lang="default"/>
-          </pm:charSpec>
-        </ext>
-      </extLst>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="4">
@@ -712,109 +659,57 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1786418752" type="1" fgLvl="100" fgClr="00C6EFCE" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF8EA9DB"/>
         <bgColor rgb="FFFFFFFF"/>
-        <extLst>
-          <ext uri="smNativeData">
-            <pm:shade xmlns:pm="smNativeData" id="1786418752" type="1" fgLvl="100" fgClr="008EA9DB" bgLvl="0" bgClr="00FFFFFF"/>
-          </ext>
-        </extLst>
       </patternFill>
     </fill>
   </fills>
   <borders count="3">
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1786418752"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1786418752"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="none">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="none">
-        <color rgb="FF000000"/>
-      </bottom>
-      <extLst>
-        <ext uri="smNativeData">
-          <pm:border xmlns:pm="smNativeData" id="1786418752"/>
-        </ext>
-      </extLst>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -823,56 +718,60 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="1" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="常规" xfId="0" builtinId="0" customBuiltin="1"/>
+    <cellStyle name="超链接" xfId="2" builtinId="8" customBuiltin="1"/>
+    <cellStyle name="好" xfId="1" builtinId="26" customBuiltin="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0"/>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
     <ext uri="smNativeData">
       <pm:charStyles xmlns:pm="smNativeData" id="1786418752" count="1">
         <pm:charStyle name="普通" fontId="0" Id="1"/>
@@ -1144,832 +1043,833 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A1:K42"/>
-  <sheetFormatPr defaultRowHeight="13.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K43"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.000000" style="5"/>
-    <col min="2" max="2" width="32.577586" customWidth="1" style="6"/>
-    <col min="3" max="3" width="26.750000" customWidth="1" style="5"/>
-    <col min="4" max="4" width="32.327586" customWidth="1" style="5"/>
-    <col min="5" max="5" width="36.163793" customWidth="1" style="6"/>
-    <col min="6" max="6" width="28.663793" customWidth="1" style="5"/>
-    <col min="7" max="8" width="18.000000" customWidth="1" style="5"/>
-    <col min="9" max="9" width="28.077586" customWidth="1" style="5"/>
-    <col min="10" max="10" width="22.500000" customWidth="1" style="5"/>
-    <col min="11" max="11" width="24.500000" customWidth="1" style="5"/>
-    <col min="12" max="16384" width="9.000000" style="5"/>
+    <col min="1" max="1" width="9" style="3"/>
+    <col min="2" max="2" width="32.58203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="36.1640625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="28.6640625" style="3" customWidth="1"/>
+    <col min="7" max="8" width="18" style="3" customWidth="1"/>
+    <col min="9" max="9" width="28.08203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="22.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="24.5" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="3" customFormat="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="3" customFormat="1">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:11" s="1" customFormat="1" ht="56" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="D3" s="3" t="s">
+      <c r="B3" s="5"/>
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:9">
-      <c r="B4" s="6" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="D4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
-      <c r="B5" s="6" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="D5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="2:9" s="4" customFormat="1">
-      <c r="B6" s="8" t="s">
+    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="D6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="2:9">
-      <c r="B7" s="6" t="s">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="2:9">
-      <c r="B8" s="6" t="s">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D8" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="D8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="2:9">
-      <c r="B9" s="6" t="s">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="D9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="2:9" s="4" customFormat="1">
-      <c r="B10" s="8" t="s">
+    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="D10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="2:9">
-      <c r="B11" s="6" t="s">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="D11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="12" spans="2:9">
-      <c r="B12" s="6" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="D12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="2:9">
-      <c r="B13" s="6" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="D13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="3" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="2:9">
-      <c r="B14" s="6" t="s">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="D14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="2:9">
-      <c r="B15" s="6" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="D15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="2:9">
-      <c r="B16" s="6" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="D16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
-      <c r="B17" s="6" t="s">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D17" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="s">
+      <c r="D17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
-      <c r="B18" s="6" t="s">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="D18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
-      <c r="B19" s="6" t="s">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B19" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="D19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
-      <c r="B20" s="6" t="s">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B20" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15" t="s">
+      <c r="D20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
-      <c r="B21" s="9" t="s">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="9" t="s">
+      <c r="D21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="2:9">
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="16" t="s">
+      <c r="D22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="3" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="2:9">
-      <c r="B23" s="10" t="s">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="D23" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="2:9">
-      <c r="B24" s="12" t="s">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B24" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="D24" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="I24" s="11" t="s">
+      <c r="I24" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="2:9">
-      <c r="B25" s="12" t="s">
+    <row r="25" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B25" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D25" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="D25" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="I25" s="11" t="s">
+      <c r="I25" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="2:9">
-      <c r="B26" s="12" t="s">
+    <row r="26" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B26" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="12" t="s">
+      <c r="D26" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="2:9">
-      <c r="B27" s="12" t="s">
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B27" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D27" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="12" t="s">
+      <c r="D27" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="I27" s="11" t="s">
+      <c r="I27" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="2:9">
-      <c r="B28" s="12" t="s">
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B28" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="12" t="s">
+      <c r="D28" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="I28" s="11" t="s">
+      <c r="I28" s="3" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="2:9">
-      <c r="B29" s="12" t="s">
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="11" t="s">
+      <c r="D29" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I29" s="11" t="s">
+      <c r="I29" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="2:9">
-      <c r="B30" s="12" t="s">
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="12" t="s">
+      <c r="D30" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="I30" s="11" t="s">
+      <c r="I30" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="2:9">
-      <c r="B31" s="13" t="s">
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="D31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="13" t="s">
+      <c r="D31" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="I31" s="14" t="s">
+      <c r="I31" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="32" spans="2:9">
-      <c r="B32" s="12" t="s">
+    <row r="32" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B32" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="12" t="s">
+      <c r="D32" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="I32" s="11" t="s">
+      <c r="I32" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="2:9">
-      <c r="B33" s="12" t="s">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="12" t="s">
+      <c r="D33" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="I33" s="11" t="s">
+      <c r="I33" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="2:9">
-      <c r="B34" s="12" t="s">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B34" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="12" t="s">
+      <c r="D34" s="3">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="I34" s="11" t="s">
+      <c r="I34" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="2:9">
-      <c r="B35" s="13" t="s">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E35" s="13" t="s">
+      <c r="E35" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="I35" s="14" t="s">
+      <c r="I35" s="9" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="36" spans="2:9">
-      <c r="B36" s="13" t="s">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B36" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E36" s="13" t="s">
+      <c r="E36" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="I36" s="14" t="s">
+      <c r="I36" s="9" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="37" spans="2:9">
-      <c r="B37" s="12" t="s">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="I37" s="11" t="s">
+      <c r="I37" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="18"/>
-      <c r="B38" s="19" t="s">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="13"/>
+      <c r="B38" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="C38" s="20" t="s">
+      <c r="C38" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="D38" s="20" t="s">
+      <c r="D38" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="E38" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
-      <c r="H38" s="18"/>
-      <c r="I38" s="20" t="s">
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="J38" s="18"/>
-      <c r="K38" s="18"/>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="18"/>
-      <c r="B39" s="19" t="s">
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39" s="14" t="s">
         <v>167</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C39" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="D39" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="18"/>
-      <c r="G39" s="18"/>
-      <c r="H39" s="18"/>
-      <c r="I39" s="20" t="s">
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="13"/>
+      <c r="I39" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="J39" s="18"/>
-      <c r="K39" s="18"/>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="18"/>
-      <c r="B40" s="19" t="s">
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="13"/>
+      <c r="B40" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C40" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="E40" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="F40" s="18"/>
-      <c r="G40" s="18"/>
-      <c r="H40" s="18"/>
-      <c r="I40" s="20" t="s">
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="J40" s="18"/>
-      <c r="K40" s="18"/>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="18"/>
-      <c r="B41" s="19" t="s">
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="13"/>
+      <c r="B41" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="C41" s="20" t="s">
+      <c r="C41" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="E41" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="20" t="s">
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="18"/>
-      <c r="B42" s="19" t="s">
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="13"/>
+      <c r="B42" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="E42" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="F42" s="18"/>
-      <c r="G42" s="18"/>
-      <c r="H42" s="18"/>
-      <c r="I42" s="20" t="s">
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+      <c r="I42" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B43" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>186</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E20" r:id="rId1"/>
-    <hyperlink ref="E22" r:id="rId2"/>
-    <hyperlink ref="E23" r:id="rId1"/>
+    <hyperlink ref="E20" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E22" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E23" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
-  <printOptions>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:pageFlags xmlns:pm="smNativeData" id="1786418752" printRowHead="0" printColHead="0" printHeadLine="0" printFootLine="0" autoHeightHeader="0" autoHeightFooter="0" fitToPageBoth="0"/>
-      </ext>
-    </extLst>
-  </printOptions>
-  <pageMargins left="0.700000" right="0.700000" top="0.750000" bottom="0.750000" header="0.300000" footer="0.300000"/>
-  <pageSetup paperSize="9" fitToWidth="0" fitToHeight="1"/>
-  <headerFooter>
-    <extLst>
-      <ext uri="smNativeData">
-        <pm:header xmlns:pm="smNativeData" id="1786418752" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="0"/>
-        <pm:footer xmlns:pm="smNativeData" id="1786418752" l="56" r="56" t="56" b="56" borderId="0" fillId="0" vertical="2"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1786418752" Id="0" type="0" value="0"/>
-        <pm:paperBin xmlns:pm="smNativeData" id="1786418752" Id="1" type="0" value="0"/>
-      </ext>
-    </extLst>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
     <ext uri="smNativeData">
       <pm:sheetPrefs xmlns:pm="smNativeData" day="1786418752" outlineProtect="1" showHorizontalRuler="1" showVerticalRuler="1" showAltShade="0">

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C9FAB5-67DE-4389-9661-3E2768470940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E194DD5-F69C-44E0-9DAF-0467EE0C5F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4020" yWindow="1330" windowWidth="37160" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2310" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="191">
   <si>
     <t>##var</t>
   </si>
@@ -592,6 +592,22 @@
   </si>
   <si>
     <t>剧情表</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbDramaCGData</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaCGData</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>DramaCGData.xlsx</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>剧情CG表</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1044,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1859,6 +1875,23 @@
       </c>
       <c r="I43" s="17" t="s">
         <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B44" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E194DD5-F69C-44E0-9DAF-0467EE0C5F39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2DF5DB-FBD7-4A34-B04E-D309861278AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2310" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="171">
   <si>
     <t>##var</t>
   </si>
@@ -517,66 +517,6 @@
   </si>
   <si>
     <t>剧情背景表</t>
-  </si>
-  <si>
-    <t>TbQuestStoryCondData</t>
-  </si>
-  <si>
-    <t>QuestStoryCondData</t>
-  </si>
-  <si>
-    <t>QuestStoryCondData.xlsx</t>
-  </si>
-  <si>
-    <t>任务/剧情状态条件表</t>
-  </si>
-  <si>
-    <t>TbQuestData</t>
-  </si>
-  <si>
-    <t>QuestDataConfig</t>
-  </si>
-  <si>
-    <t>QuestDataConfig.xlsx</t>
-  </si>
-  <si>
-    <t>任务配置表</t>
-  </si>
-  <si>
-    <t>TbQuestObjData</t>
-  </si>
-  <si>
-    <t>QuestObjConfig</t>
-  </si>
-  <si>
-    <t>QuestObjConfig.xlsx</t>
-  </si>
-  <si>
-    <t>任务目标配置表</t>
-  </si>
-  <si>
-    <t>TbQuestCategoryData</t>
-  </si>
-  <si>
-    <t>QuestCategoryData</t>
-  </si>
-  <si>
-    <t>QuestCategoryData.xlsx</t>
-  </si>
-  <si>
-    <t>任务类别配置表</t>
-  </si>
-  <si>
-    <t>TbQuestRewardData</t>
-  </si>
-  <si>
-    <t>QuestRewardData</t>
-  </si>
-  <si>
-    <t>QuestRewardData.xlsx</t>
-  </si>
-  <si>
-    <t>任务奖励展示配置表</t>
   </si>
   <si>
     <t>TbDramaData</t>
@@ -626,29 +566,34 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -718,7 +663,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -756,12 +701,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1060,7 +999,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1660,7 +1599,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
         <v>142</v>
       </c>
@@ -1677,7 +1616,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
         <v>146</v>
       </c>
@@ -1694,7 +1633,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="s">
         <v>150</v>
       </c>
@@ -1711,7 +1650,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B36" s="8" t="s">
         <v>155</v>
       </c>
@@ -1728,7 +1667,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
         <v>159</v>
       </c>
@@ -1745,153 +1684,38 @@
         <v>162</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="14" t="s">
         <v>163</v>
       </c>
       <c r="C38" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="13" t="s">
         <v>152</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>165</v>
       </c>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
       <c r="I38" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="14" t="s">
         <v>167</v>
       </c>
       <c r="C39" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="13" t="s">
         <v>152</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="F39" s="13"/>
-      <c r="G39" s="13"/>
-      <c r="H39" s="13"/>
       <c r="I39" s="15" t="s">
         <v>170</v>
-      </c>
-      <c r="J39" s="13"/>
-      <c r="K39" s="13"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E40" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="F40" s="13"/>
-      <c r="G40" s="13"/>
-      <c r="H40" s="13"/>
-      <c r="I40" s="15" t="s">
-        <v>174</v>
-      </c>
-      <c r="J40" s="13"/>
-      <c r="K40" s="13"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>176</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E41" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="F41" s="13"/>
-      <c r="G41" s="13"/>
-      <c r="H41" s="13"/>
-      <c r="I41" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="J41" s="13"/>
-      <c r="K41" s="13"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>180</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E42" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="F42" s="13"/>
-      <c r="G42" s="13"/>
-      <c r="H42" s="13"/>
-      <c r="I42" s="15" t="s">
-        <v>182</v>
-      </c>
-      <c r="J42" s="13"/>
-      <c r="K42" s="13"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B43" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C43" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="I43" s="17" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B44" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="I44" s="17" t="s">
-        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\Unity\Project\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE2DF5DB-FBD7-4A34-B04E-D309861278AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FC6FED-CFEA-40BE-94D1-3DDA8E2D0085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="28800" windowHeight="15370" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2310" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="167">
   <si>
     <t>##var</t>
   </si>
@@ -109,18 +109,6 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>TbDialogueData</t>
-  </si>
-  <si>
-    <t>DialogueData</t>
-  </si>
-  <si>
-    <t>DialogueData.xlsx</t>
-  </si>
-  <si>
-    <t>游戏对话配置数据</t>
   </si>
   <si>
     <t>TbNpcData</t>
@@ -566,34 +554,29 @@
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="等线"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
-      <charset val="134"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="等线"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
@@ -999,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1116,44 +1099,44 @@
       <c r="D4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>29</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="D5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="6" t="s">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="D6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" s="3" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1191,37 +1174,37 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="4" t="s">
+    <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="D9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="I10" s="3" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1232,7 +1215,7 @@
       <c r="C11" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D11" s="2" t="b">
+      <c r="D11" s="3" t="b">
         <v>1</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -1371,7 +1354,7 @@
       <c r="D19" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="10" t="s">
         <v>89</v>
       </c>
       <c r="I19" s="3" t="s">
@@ -1379,7 +1362,7 @@
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="7" t="s">
         <v>91</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1388,7 +1371,7 @@
       <c r="D20" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="7" t="s">
         <v>93</v>
       </c>
       <c r="I20" s="3" t="s">
@@ -1405,32 +1388,32 @@
       <c r="D21" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="11" t="s">
         <v>97</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="11" t="s">
+      <c r="I22" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>98</v>
-      </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="4" t="s">
         <v>102</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1439,7 +1422,7 @@
       <c r="D23" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="4" t="s">
         <v>104</v>
       </c>
       <c r="I23" s="3" t="s">
@@ -1524,7 +1507,7 @@
       <c r="D28" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>124</v>
       </c>
       <c r="I28" s="3" t="s">
@@ -1541,7 +1524,7 @@
       <c r="D29" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="4" t="s">
         <v>128</v>
       </c>
       <c r="I29" s="3" t="s">
@@ -1549,36 +1532,36 @@
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C30" s="9" t="s">
         <v>131</v>
       </c>
       <c r="D30" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="I30" s="3" t="s">
+      <c r="I30" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="3" t="s">
         <v>135</v>
       </c>
       <c r="D31" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="I31" s="9" t="s">
+      <c r="I31" s="3" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1606,7 +1589,7 @@
       <c r="C33" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D33" s="3" t="b">
+      <c r="D33" s="3">
         <v>1</v>
       </c>
       <c r="E33" s="4" t="s">
@@ -1617,31 +1600,31 @@
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C34" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="D34" s="3">
-        <v>1</v>
-      </c>
-      <c r="E34" s="4" t="s">
+      <c r="D34" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="E34" s="8" t="s">
         <v>149</v>
+      </c>
+      <c r="I34" s="9" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B35" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>153</v>
@@ -1651,36 +1634,36 @@
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="3" t="s">
         <v>156</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E36" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E36" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="I36" s="9" t="s">
+      <c r="I36" s="3" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="D37" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E37" s="4" t="s">
+      <c r="D37" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="E37" s="14" t="s">
         <v>161</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="15" t="s">
         <v>162</v>
       </c>
     </row>
@@ -1692,38 +1675,21 @@
         <v>164</v>
       </c>
       <c r="D38" s="13" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>165</v>
       </c>
       <c r="I38" s="15" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="E39" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="I39" s="15" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E20" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="E22" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="E23" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="E19" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E21" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="E22" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0"/>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84FC6FED-CFEA-40BE-94D1-3DDA8E2D0085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FA627A-9AC3-450A-8279-4887836F3B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2310" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4450" yWindow="2240" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="175">
   <si>
     <t>##var</t>
   </si>
@@ -537,6 +537,30 @@
   <si>
     <t>剧情CG表</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>TbTutorialData</t>
+  </si>
+  <si>
+    <t>TutorialData</t>
+  </si>
+  <si>
+    <t>TutorialData.xlsx</t>
+  </si>
+  <si>
+    <t>引导流程表</t>
+  </si>
+  <si>
+    <t>TbTutorialStepData</t>
+  </si>
+  <si>
+    <t>TutorialStepData</t>
+  </si>
+  <si>
+    <t>TutorialStepData.xlsx</t>
+  </si>
+  <si>
+    <t>引导步骤表</t>
   </si>
 </sst>
 </file>
@@ -982,7 +1006,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1682,6 +1706,40 @@
       </c>
       <c r="I38" s="15" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B39" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="I39" s="9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B40" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D40" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98FA627A-9AC3-450A-8279-4887836F3B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39906AA3-8FF6-4E2C-AE82-07DB47B59E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4450" yWindow="2240" windowWidth="44100" windowHeight="18570" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="6320" windowWidth="44100" windowHeight="14560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="167">
   <si>
     <t>##var</t>
   </si>
@@ -537,30 +537,6 @@
   <si>
     <t>剧情CG表</t>
     <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbTutorialData</t>
-  </si>
-  <si>
-    <t>TutorialData</t>
-  </si>
-  <si>
-    <t>TutorialData.xlsx</t>
-  </si>
-  <si>
-    <t>引导流程表</t>
-  </si>
-  <si>
-    <t>TbTutorialStepData</t>
-  </si>
-  <si>
-    <t>TutorialStepData</t>
-  </si>
-  <si>
-    <t>TutorialStepData.xlsx</t>
-  </si>
-  <si>
-    <t>引导步骤表</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +982,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
@@ -1706,40 +1682,6 @@
       </c>
       <c r="I38" s="15" t="s">
         <v>166</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="C39" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="D39" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="I39" s="9" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="D40" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="I40" s="9" t="s">
-        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLab\RAFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB49644-202C-4C9C-A562-3C680E9944DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854BB8CD-A486-45EC-9C68-C1D5F236C6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="3200" windowWidth="44100" windowHeight="14560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57600" yWindow="5085" windowWidth="66150" windowHeight="21840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -109,65 +109,6 @@
   </si>
   <si>
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
-  </si>
-  <si>
-    <t>TbUIPageData</t>
-  </si>
-  <si>
-    <t>UIPageData</t>
-  </si>
-  <si>
-    <t>UIPageData.xlsx</t>
-  </si>
-  <si>
-    <t>UI界面配置表</t>
-  </si>
-  <si>
-    <t>TbItemData</t>
-  </si>
-  <si>
-    <t>ItemData</t>
-  </si>
-  <si>
-    <t>ItemData@ItemData.xlsx</t>
-  </si>
-  <si>
-    <t>道具配置表</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>TbDramaData</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DramaData</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DramaData.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>剧情表</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TbDramaCGData</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DramaCGData</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>DramaCGData.xlsx</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>剧情CG表</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -696,79 +637,32 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
     <row r="5" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
-      <c r="B5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
-      <c r="I5" s="3" t="s">
-        <v>34</v>
-      </c>
+      <c r="I5" s="3"/>
       <c r="J5" s="3"/>
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>39</v>
-      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="8"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>43</v>
-      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="8"/>
+      <c r="I7" s="9"/>
     </row>
     <row r="9" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
@@ -785,9 +679,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="E5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0"/>
   <extLst>
